--- a/artfynd/A 22588-2025 artfynd.xlsx
+++ b/artfynd/A 22588-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125229319</v>
       </c>
       <c r="B2" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 22588-2025 artfynd.xlsx
+++ b/artfynd/A 22588-2025 artfynd.xlsx
@@ -1090,7 +1090,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125710815</v>
+        <v>125710723</v>
       </c>
       <c r="B6" t="n">
         <v>98324</v>
@@ -1118,20 +1118,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hamrasjöhötjärnen, Hamrasjöhötjärnen, Dlr</t>
+          <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>496225</v>
+        <v>496089</v>
       </c>
       <c r="R6" t="n">
-        <v>6830300</v>
+        <v>6830292</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1175,12 +1184,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1284,7 +1293,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125710723</v>
+        <v>125710815</v>
       </c>
       <c r="B8" t="n">
         <v>98324</v>
@@ -1312,29 +1321,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Rickosennoppi, Rickosennoppi, Dlr</t>
+          <t>Hamrasjöhötjärnen, Hamrasjöhötjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>496089</v>
+        <v>496225</v>
       </c>
       <c r="R8" t="n">
-        <v>6830292</v>
+        <v>6830300</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1378,12 +1378,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1584,10 +1584,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125709968</v>
+        <v>125710052</v>
       </c>
       <c r="B11" t="n">
-        <v>78634</v>
+        <v>78726</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1595,34 +1595,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Rickosennoppi, Rickosennoppi, Dlr</t>
+          <t>Åtjärnen, Åtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>495640</v>
+        <v>495635</v>
       </c>
       <c r="R11" t="n">
-        <v>6830078</v>
+        <v>6830098</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1669,22 +1669,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125710052</v>
+        <v>125709968</v>
       </c>
       <c r="B12" t="n">
-        <v>78726</v>
+        <v>78634</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1692,34 +1692,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Åtjärnen, Åtjärnen, Dlr</t>
+          <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>495635</v>
+        <v>495640</v>
       </c>
       <c r="R12" t="n">
-        <v>6830098</v>
+        <v>6830078</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1766,12 +1766,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 22588-2025 artfynd.xlsx
+++ b/artfynd/A 22588-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125229319</v>
       </c>
       <c r="B2" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125709664</v>
+        <v>125710600</v>
       </c>
       <c r="B3" t="n">
-        <v>79585</v>
+        <v>78726</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -796,37 +796,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Rickosennoppi, Rickosennoppi, Dlr</t>
+          <t>Hamrasjöhötjärnen, Hamrasjöhötjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>495466</v>
+        <v>496171</v>
       </c>
       <c r="R3" t="n">
-        <v>6830109</v>
+        <v>6830337</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,60 +870,69 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125710600</v>
+        <v>125711283</v>
       </c>
       <c r="B4" t="n">
-        <v>78726</v>
+        <v>98331</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hamrasjöhötjärnen, Hamrasjöhötjärnen, Dlr</t>
+          <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>496171</v>
+        <v>495823</v>
       </c>
       <c r="R4" t="n">
-        <v>6830337</v>
+        <v>6830334</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -953,6 +962,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Inom anmälan A-22588-2025.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -967,66 +981,57 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125711283</v>
+        <v>125709664</v>
       </c>
       <c r="B5" t="n">
-        <v>98324</v>
+        <v>79585</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>495823</v>
+        <v>495466</v>
       </c>
       <c r="R5" t="n">
-        <v>6830334</v>
+        <v>6830109</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1059,11 +1064,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Inom anmälan A-22588-2025.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1090,54 +1090,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125710723</v>
+        <v>125710065</v>
       </c>
       <c r="B6" t="n">
-        <v>98324</v>
+        <v>78634</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>496089</v>
+        <v>495658</v>
       </c>
       <c r="R6" t="n">
-        <v>6830292</v>
+        <v>6830096</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1196,45 +1187,54 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125710065</v>
+        <v>125710723</v>
       </c>
       <c r="B7" t="n">
-        <v>78634</v>
+        <v>98331</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>495658</v>
+        <v>496089</v>
       </c>
       <c r="R7" t="n">
-        <v>6830096</v>
+        <v>6830292</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1296,7 +1296,7 @@
         <v>125710815</v>
       </c>
       <c r="B8" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1584,10 +1584,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125710052</v>
+        <v>125709968</v>
       </c>
       <c r="B11" t="n">
-        <v>78726</v>
+        <v>78634</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1595,34 +1595,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Åtjärnen, Åtjärnen, Dlr</t>
+          <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>495635</v>
+        <v>495640</v>
       </c>
       <c r="R11" t="n">
-        <v>6830098</v>
+        <v>6830078</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1669,22 +1669,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125709968</v>
+        <v>125710052</v>
       </c>
       <c r="B12" t="n">
-        <v>78634</v>
+        <v>78726</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1692,34 +1692,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Rickosennoppi, Rickosennoppi, Dlr</t>
+          <t>Åtjärnen, Åtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>495640</v>
+        <v>495635</v>
       </c>
       <c r="R12" t="n">
-        <v>6830078</v>
+        <v>6830098</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1766,22 +1766,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125710983</v>
+        <v>125709636</v>
       </c>
       <c r="B13" t="n">
-        <v>78967</v>
+        <v>78726</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1789,37 +1789,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Hamrasjöhötjärnen, Hamrasjöhötjärnen, Dlr</t>
+          <t>Åtjärnen, Åtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>496064</v>
+        <v>495478</v>
       </c>
       <c r="R13" t="n">
-        <v>6830327</v>
+        <v>6830082</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1875,10 +1875,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125709636</v>
+        <v>125710983</v>
       </c>
       <c r="B14" t="n">
-        <v>78726</v>
+        <v>78967</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1886,37 +1886,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Åtjärnen, Åtjärnen, Dlr</t>
+          <t>Hamrasjöhötjärnen, Hamrasjöhötjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>495478</v>
+        <v>496064</v>
       </c>
       <c r="R14" t="n">
-        <v>6830082</v>
+        <v>6830327</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         <v>125710834</v>
       </c>
       <c r="B16" t="n">
-        <v>91220</v>
+        <v>91227</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2263,10 +2263,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125711527</v>
+        <v>125710845</v>
       </c>
       <c r="B18" t="n">
-        <v>98345</v>
+        <v>91192</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2274,21 +2274,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221952</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2298,10 +2298,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>495738</v>
+        <v>496132</v>
       </c>
       <c r="R18" t="n">
-        <v>6830297</v>
+        <v>6830383</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2360,10 +2360,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125710845</v>
+        <v>125711527</v>
       </c>
       <c r="B19" t="n">
-        <v>91185</v>
+        <v>98352</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2371,21 +2371,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>221952</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2395,10 +2395,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>496132</v>
+        <v>495738</v>
       </c>
       <c r="R19" t="n">
-        <v>6830383</v>
+        <v>6830297</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 22588-2025 artfynd.xlsx
+++ b/artfynd/A 22588-2025 artfynd.xlsx
@@ -1778,10 +1778,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125709636</v>
+        <v>125710983</v>
       </c>
       <c r="B13" t="n">
-        <v>78726</v>
+        <v>78967</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1789,37 +1789,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Åtjärnen, Åtjärnen, Dlr</t>
+          <t>Hamrasjöhötjärnen, Hamrasjöhötjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>495478</v>
+        <v>496064</v>
       </c>
       <c r="R13" t="n">
-        <v>6830082</v>
+        <v>6830327</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1875,10 +1875,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125710983</v>
+        <v>125709636</v>
       </c>
       <c r="B14" t="n">
-        <v>78967</v>
+        <v>78726</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1886,37 +1886,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Hamrasjöhötjärnen, Hamrasjöhötjärnen, Dlr</t>
+          <t>Åtjärnen, Åtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>496064</v>
+        <v>495478</v>
       </c>
       <c r="R14" t="n">
-        <v>6830327</v>
+        <v>6830082</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2263,10 +2263,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125710845</v>
+        <v>125711527</v>
       </c>
       <c r="B18" t="n">
-        <v>91192</v>
+        <v>98352</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2274,21 +2274,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>221952</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2298,10 +2298,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>496132</v>
+        <v>495738</v>
       </c>
       <c r="R18" t="n">
-        <v>6830383</v>
+        <v>6830297</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2360,10 +2360,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125711527</v>
+        <v>125710845</v>
       </c>
       <c r="B19" t="n">
-        <v>98352</v>
+        <v>91192</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2371,21 +2371,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221952</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2395,10 +2395,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>495738</v>
+        <v>496132</v>
       </c>
       <c r="R19" t="n">
-        <v>6830297</v>
+        <v>6830383</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 22588-2025 artfynd.xlsx
+++ b/artfynd/A 22588-2025 artfynd.xlsx
@@ -785,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125710600</v>
+        <v>125709664</v>
       </c>
       <c r="B3" t="n">
-        <v>78726</v>
+        <v>79585</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -796,37 +796,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hamrasjöhötjärnen, Hamrasjöhötjärnen, Dlr</t>
+          <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>496171</v>
+        <v>495466</v>
       </c>
       <c r="R3" t="n">
-        <v>6830337</v>
+        <v>6830109</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,12 +870,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125709664</v>
+        <v>125710600</v>
       </c>
       <c r="B5" t="n">
-        <v>79585</v>
+        <v>78726</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1004,37 +1004,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Rickosennoppi, Rickosennoppi, Dlr</t>
+          <t>Hamrasjöhötjärnen, Hamrasjöhötjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>495466</v>
+        <v>496171</v>
       </c>
       <c r="R5" t="n">
-        <v>6830109</v>
+        <v>6830337</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1078,12 +1078,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1584,10 +1584,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125709968</v>
+        <v>125710052</v>
       </c>
       <c r="B11" t="n">
-        <v>78634</v>
+        <v>78726</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1595,34 +1595,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Rickosennoppi, Rickosennoppi, Dlr</t>
+          <t>Åtjärnen, Åtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>495640</v>
+        <v>495635</v>
       </c>
       <c r="R11" t="n">
-        <v>6830078</v>
+        <v>6830098</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1669,22 +1669,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125710052</v>
+        <v>125709968</v>
       </c>
       <c r="B12" t="n">
-        <v>78726</v>
+        <v>78634</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1692,34 +1692,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Åtjärnen, Åtjärnen, Dlr</t>
+          <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>495635</v>
+        <v>495640</v>
       </c>
       <c r="R12" t="n">
-        <v>6830098</v>
+        <v>6830078</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1766,12 +1766,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 22588-2025 artfynd.xlsx
+++ b/artfynd/A 22588-2025 artfynd.xlsx
@@ -785,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125709664</v>
+        <v>125710600</v>
       </c>
       <c r="B3" t="n">
-        <v>79585</v>
+        <v>78727</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -796,37 +796,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Rickosennoppi, Rickosennoppi, Dlr</t>
+          <t>Hamrasjöhötjärnen, Hamrasjöhötjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>495466</v>
+        <v>496171</v>
       </c>
       <c r="R3" t="n">
-        <v>6830109</v>
+        <v>6830337</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,66 +870,57 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125711283</v>
+        <v>125709664</v>
       </c>
       <c r="B4" t="n">
-        <v>98331</v>
+        <v>79586</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>495823</v>
+        <v>495466</v>
       </c>
       <c r="R4" t="n">
-        <v>6830334</v>
+        <v>6830109</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -962,11 +953,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Inom anmälan A-22588-2025.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -993,48 +979,57 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125710600</v>
+        <v>125711283</v>
       </c>
       <c r="B5" t="n">
-        <v>78726</v>
+        <v>98334</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hamrasjöhötjärnen, Hamrasjöhötjärnen, Dlr</t>
+          <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>496171</v>
+        <v>495823</v>
       </c>
       <c r="R5" t="n">
-        <v>6830337</v>
+        <v>6830334</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1064,6 +1059,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Inom anmälan A-22588-2025.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1078,12 +1078,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1093,7 +1093,7 @@
         <v>125710065</v>
       </c>
       <c r="B6" t="n">
-        <v>78634</v>
+        <v>78635</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1187,10 +1187,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125710723</v>
+        <v>125710815</v>
       </c>
       <c r="B7" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1215,29 +1215,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Rickosennoppi, Rickosennoppi, Dlr</t>
+          <t>Hamrasjöhötjärnen, Hamrasjöhötjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>496089</v>
+        <v>496225</v>
       </c>
       <c r="R7" t="n">
-        <v>6830292</v>
+        <v>6830300</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1281,22 +1272,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125710815</v>
+        <v>125710723</v>
       </c>
       <c r="B8" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1321,20 +1312,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hamrasjöhötjärnen, Hamrasjöhötjärnen, Dlr</t>
+          <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>496225</v>
+        <v>496089</v>
       </c>
       <c r="R8" t="n">
-        <v>6830300</v>
+        <v>6830292</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1378,12 +1378,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1393,7 +1393,7 @@
         <v>125709668</v>
       </c>
       <c r="B9" t="n">
-        <v>78634</v>
+        <v>78635</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         <v>125711141</v>
       </c>
       <c r="B10" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1584,10 +1584,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125710052</v>
+        <v>125709968</v>
       </c>
       <c r="B11" t="n">
-        <v>78726</v>
+        <v>78635</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1595,34 +1595,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Åtjärnen, Åtjärnen, Dlr</t>
+          <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>495635</v>
+        <v>495640</v>
       </c>
       <c r="R11" t="n">
-        <v>6830098</v>
+        <v>6830078</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1669,22 +1669,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125709968</v>
+        <v>125710052</v>
       </c>
       <c r="B12" t="n">
-        <v>78634</v>
+        <v>78727</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1692,34 +1692,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Rickosennoppi, Rickosennoppi, Dlr</t>
+          <t>Åtjärnen, Åtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>495640</v>
+        <v>495635</v>
       </c>
       <c r="R12" t="n">
-        <v>6830078</v>
+        <v>6830098</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1766,22 +1766,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125710983</v>
+        <v>125709636</v>
       </c>
       <c r="B13" t="n">
-        <v>78967</v>
+        <v>78727</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1789,37 +1789,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Hamrasjöhötjärnen, Hamrasjöhötjärnen, Dlr</t>
+          <t>Åtjärnen, Åtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>496064</v>
+        <v>495478</v>
       </c>
       <c r="R13" t="n">
-        <v>6830327</v>
+        <v>6830082</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1875,10 +1875,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125709636</v>
+        <v>125710983</v>
       </c>
       <c r="B14" t="n">
-        <v>78726</v>
+        <v>78968</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1886,37 +1886,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Åtjärnen, Åtjärnen, Dlr</t>
+          <t>Hamrasjöhötjärnen, Hamrasjöhötjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>495478</v>
+        <v>496064</v>
       </c>
       <c r="R14" t="n">
-        <v>6830082</v>
+        <v>6830327</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         <v>125709679</v>
       </c>
       <c r="B15" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         <v>125710834</v>
       </c>
       <c r="B16" t="n">
-        <v>91227</v>
+        <v>91228</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
         <v>125710111</v>
       </c>
       <c r="B17" t="n">
-        <v>78726</v>
+        <v>78727</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2263,10 +2263,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125711527</v>
+        <v>125710845</v>
       </c>
       <c r="B18" t="n">
-        <v>98352</v>
+        <v>91193</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2274,21 +2274,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221952</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2298,10 +2298,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>495738</v>
+        <v>496132</v>
       </c>
       <c r="R18" t="n">
-        <v>6830297</v>
+        <v>6830383</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2360,10 +2360,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125710845</v>
+        <v>125711527</v>
       </c>
       <c r="B19" t="n">
-        <v>91192</v>
+        <v>98355</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2371,21 +2371,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>221952</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2395,10 +2395,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>496132</v>
+        <v>495738</v>
       </c>
       <c r="R19" t="n">
-        <v>6830383</v>
+        <v>6830297</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 22588-2025 artfynd.xlsx
+++ b/artfynd/A 22588-2025 artfynd.xlsx
@@ -1778,10 +1778,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125709636</v>
+        <v>125710983</v>
       </c>
       <c r="B13" t="n">
-        <v>78727</v>
+        <v>78968</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1789,37 +1789,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Åtjärnen, Åtjärnen, Dlr</t>
+          <t>Hamrasjöhötjärnen, Hamrasjöhötjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>495478</v>
+        <v>496064</v>
       </c>
       <c r="R13" t="n">
-        <v>6830082</v>
+        <v>6830327</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1875,10 +1875,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125710983</v>
+        <v>125709636</v>
       </c>
       <c r="B14" t="n">
-        <v>78968</v>
+        <v>78727</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1886,37 +1886,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Hamrasjöhötjärnen, Hamrasjöhötjärnen, Dlr</t>
+          <t>Åtjärnen, Åtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>496064</v>
+        <v>495478</v>
       </c>
       <c r="R14" t="n">
-        <v>6830327</v>
+        <v>6830082</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>

--- a/artfynd/A 22588-2025 artfynd.xlsx
+++ b/artfynd/A 22588-2025 artfynd.xlsx
@@ -785,48 +785,57 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125710600</v>
+        <v>125711283</v>
       </c>
       <c r="B3" t="n">
-        <v>78727</v>
+        <v>98338</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hamrasjöhötjärnen, Hamrasjöhötjärnen, Dlr</t>
+          <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>496171</v>
+        <v>495823</v>
       </c>
       <c r="R3" t="n">
-        <v>6830337</v>
+        <v>6830334</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -856,6 +865,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Inom anmälan A-22588-2025.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -870,22 +884,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125709664</v>
+        <v>125710600</v>
       </c>
       <c r="B4" t="n">
-        <v>79586</v>
+        <v>78731</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -893,37 +907,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Rickosennoppi, Rickosennoppi, Dlr</t>
+          <t>Hamrasjöhötjärnen, Hamrasjöhötjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>495466</v>
+        <v>496171</v>
       </c>
       <c r="R4" t="n">
-        <v>6830109</v>
+        <v>6830337</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -967,66 +981,57 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125711283</v>
+        <v>125709664</v>
       </c>
       <c r="B5" t="n">
-        <v>98334</v>
+        <v>79590</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>495823</v>
+        <v>495466</v>
       </c>
       <c r="R5" t="n">
-        <v>6830334</v>
+        <v>6830109</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1059,11 +1064,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Inom anmälan A-22588-2025.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1090,48 +1090,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125710065</v>
+        <v>125710815</v>
       </c>
       <c r="B6" t="n">
-        <v>78635</v>
+        <v>98338</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Rickosennoppi, Rickosennoppi, Dlr</t>
+          <t>Hamrasjöhötjärnen, Hamrasjöhötjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>495658</v>
+        <v>496225</v>
       </c>
       <c r="R6" t="n">
-        <v>6830096</v>
+        <v>6830300</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1175,22 +1175,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125710815</v>
+        <v>125710723</v>
       </c>
       <c r="B7" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1215,20 +1215,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hamrasjöhötjärnen, Hamrasjöhötjärnen, Dlr</t>
+          <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>496225</v>
+        <v>496089</v>
       </c>
       <c r="R7" t="n">
-        <v>6830300</v>
+        <v>6830292</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1272,66 +1281,57 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125710723</v>
+        <v>125710065</v>
       </c>
       <c r="B8" t="n">
-        <v>98334</v>
+        <v>78639</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>496089</v>
+        <v>495658</v>
       </c>
       <c r="R8" t="n">
-        <v>6830292</v>
+        <v>6830096</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1393,7 +1393,7 @@
         <v>125709668</v>
       </c>
       <c r="B9" t="n">
-        <v>78635</v>
+        <v>78639</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         <v>125711141</v>
       </c>
       <c r="B10" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1584,10 +1584,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125709968</v>
+        <v>125710052</v>
       </c>
       <c r="B11" t="n">
-        <v>78635</v>
+        <v>78731</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1595,34 +1595,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Rickosennoppi, Rickosennoppi, Dlr</t>
+          <t>Åtjärnen, Åtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>495640</v>
+        <v>495635</v>
       </c>
       <c r="R11" t="n">
-        <v>6830078</v>
+        <v>6830098</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1669,22 +1669,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125710052</v>
+        <v>125709968</v>
       </c>
       <c r="B12" t="n">
-        <v>78727</v>
+        <v>78639</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1692,34 +1692,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Åtjärnen, Åtjärnen, Dlr</t>
+          <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>495635</v>
+        <v>495640</v>
       </c>
       <c r="R12" t="n">
-        <v>6830098</v>
+        <v>6830078</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1766,12 +1766,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1781,7 +1781,7 @@
         <v>125710983</v>
       </c>
       <c r="B13" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1878,7 +1878,7 @@
         <v>125709636</v>
       </c>
       <c r="B14" t="n">
-        <v>78727</v>
+        <v>78731</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         <v>125709679</v>
       </c>
       <c r="B15" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         <v>125710834</v>
       </c>
       <c r="B16" t="n">
-        <v>91228</v>
+        <v>91232</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
         <v>125710111</v>
       </c>
       <c r="B17" t="n">
-        <v>78727</v>
+        <v>78731</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
         <v>125710845</v>
       </c>
       <c r="B18" t="n">
-        <v>91193</v>
+        <v>91197</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>125711527</v>
       </c>
       <c r="B19" t="n">
-        <v>98355</v>
+        <v>98359</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 22588-2025 artfynd.xlsx
+++ b/artfynd/A 22588-2025 artfynd.xlsx
@@ -1090,48 +1090,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125710815</v>
+        <v>125710065</v>
       </c>
       <c r="B6" t="n">
-        <v>98338</v>
+        <v>78639</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hamrasjöhötjärnen, Hamrasjöhötjärnen, Dlr</t>
+          <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>496225</v>
+        <v>495658</v>
       </c>
       <c r="R6" t="n">
-        <v>6830300</v>
+        <v>6830096</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1175,19 +1175,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125710723</v>
+        <v>125710815</v>
       </c>
       <c r="B7" t="n">
         <v>98338</v>
@@ -1215,29 +1215,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Rickosennoppi, Rickosennoppi, Dlr</t>
+          <t>Hamrasjöhötjärnen, Hamrasjöhötjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>496089</v>
+        <v>496225</v>
       </c>
       <c r="R7" t="n">
-        <v>6830292</v>
+        <v>6830300</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1281,57 +1272,66 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125710065</v>
+        <v>125710723</v>
       </c>
       <c r="B8" t="n">
-        <v>78639</v>
+        <v>98338</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>495658</v>
+        <v>496089</v>
       </c>
       <c r="R8" t="n">
-        <v>6830096</v>
+        <v>6830292</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1584,10 +1584,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125710052</v>
+        <v>125709968</v>
       </c>
       <c r="B11" t="n">
-        <v>78731</v>
+        <v>78639</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1595,34 +1595,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Åtjärnen, Åtjärnen, Dlr</t>
+          <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>495635</v>
+        <v>495640</v>
       </c>
       <c r="R11" t="n">
-        <v>6830098</v>
+        <v>6830078</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1669,22 +1669,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125709968</v>
+        <v>125710052</v>
       </c>
       <c r="B12" t="n">
-        <v>78639</v>
+        <v>78731</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1692,34 +1692,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Rickosennoppi, Rickosennoppi, Dlr</t>
+          <t>Åtjärnen, Åtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>495640</v>
+        <v>495635</v>
       </c>
       <c r="R12" t="n">
-        <v>6830078</v>
+        <v>6830098</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1766,12 +1766,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 22588-2025 artfynd.xlsx
+++ b/artfynd/A 22588-2025 artfynd.xlsx
@@ -785,54 +785,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125711283</v>
+        <v>125709664</v>
       </c>
       <c r="B3" t="n">
-        <v>98338</v>
+        <v>79590</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>495823</v>
+        <v>495466</v>
       </c>
       <c r="R3" t="n">
-        <v>6830334</v>
+        <v>6830109</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,11 +856,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Inom anmälan A-22588-2025.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -993,45 +979,54 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125709664</v>
+        <v>125711283</v>
       </c>
       <c r="B5" t="n">
-        <v>79590</v>
+        <v>98339</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>495466</v>
+        <v>495823</v>
       </c>
       <c r="R5" t="n">
-        <v>6830109</v>
+        <v>6830334</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1064,6 +1059,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Inom anmälan A-22588-2025.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1187,10 +1187,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125710815</v>
+        <v>125710723</v>
       </c>
       <c r="B7" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1215,20 +1215,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hamrasjöhötjärnen, Hamrasjöhötjärnen, Dlr</t>
+          <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>496225</v>
+        <v>496089</v>
       </c>
       <c r="R7" t="n">
-        <v>6830300</v>
+        <v>6830292</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1272,22 +1281,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125710723</v>
+        <v>125710815</v>
       </c>
       <c r="B8" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1312,29 +1321,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Rickosennoppi, Rickosennoppi, Dlr</t>
+          <t>Hamrasjöhötjärnen, Hamrasjöhötjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>496089</v>
+        <v>496225</v>
       </c>
       <c r="R8" t="n">
-        <v>6830292</v>
+        <v>6830300</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1378,12 +1378,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1584,10 +1584,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125709968</v>
+        <v>125710052</v>
       </c>
       <c r="B11" t="n">
-        <v>78639</v>
+        <v>78731</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1595,34 +1595,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Rickosennoppi, Rickosennoppi, Dlr</t>
+          <t>Åtjärnen, Åtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>495640</v>
+        <v>495635</v>
       </c>
       <c r="R11" t="n">
-        <v>6830078</v>
+        <v>6830098</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1669,22 +1669,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125710052</v>
+        <v>125709968</v>
       </c>
       <c r="B12" t="n">
-        <v>78731</v>
+        <v>78639</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1692,34 +1692,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Åtjärnen, Åtjärnen, Dlr</t>
+          <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>495635</v>
+        <v>495640</v>
       </c>
       <c r="R12" t="n">
-        <v>6830098</v>
+        <v>6830078</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1766,12 +1766,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2363,7 +2363,7 @@
         <v>125711527</v>
       </c>
       <c r="B19" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 22588-2025 artfynd.xlsx
+++ b/artfynd/A 22588-2025 artfynd.xlsx
@@ -785,45 +785,54 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125709664</v>
+        <v>125711283</v>
       </c>
       <c r="B3" t="n">
-        <v>79590</v>
+        <v>98339</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>495466</v>
+        <v>495823</v>
       </c>
       <c r="R3" t="n">
-        <v>6830109</v>
+        <v>6830334</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -856,6 +865,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Inom anmälan A-22588-2025.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -882,10 +896,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125710600</v>
+        <v>125709664</v>
       </c>
       <c r="B4" t="n">
-        <v>78731</v>
+        <v>79590</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -893,37 +907,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hamrasjöhötjärnen, Hamrasjöhötjärnen, Dlr</t>
+          <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>496171</v>
+        <v>495466</v>
       </c>
       <c r="R4" t="n">
-        <v>6830337</v>
+        <v>6830109</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -967,69 +981,60 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125711283</v>
+        <v>125710600</v>
       </c>
       <c r="B5" t="n">
-        <v>98339</v>
+        <v>78731</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Rickosennoppi, Rickosennoppi, Dlr</t>
+          <t>Hamrasjöhötjärnen, Hamrasjöhötjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>495823</v>
+        <v>496171</v>
       </c>
       <c r="R5" t="n">
-        <v>6830334</v>
+        <v>6830337</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1059,11 +1064,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Inom anmälan A-22588-2025.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1078,12 +1078,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 22588-2025 artfynd.xlsx
+++ b/artfynd/A 22588-2025 artfynd.xlsx
@@ -1090,45 +1090,54 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125710065</v>
+        <v>125710723</v>
       </c>
       <c r="B6" t="n">
-        <v>78639</v>
+        <v>98339</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>495658</v>
+        <v>496089</v>
       </c>
       <c r="R6" t="n">
-        <v>6830096</v>
+        <v>6830292</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1187,7 +1196,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125710723</v>
+        <v>125710815</v>
       </c>
       <c r="B7" t="n">
         <v>98339</v>
@@ -1215,29 +1224,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Rickosennoppi, Rickosennoppi, Dlr</t>
+          <t>Hamrasjöhötjärnen, Hamrasjöhötjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>496089</v>
+        <v>496225</v>
       </c>
       <c r="R7" t="n">
-        <v>6830292</v>
+        <v>6830300</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1281,60 +1281,60 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125710815</v>
+        <v>125710065</v>
       </c>
       <c r="B8" t="n">
-        <v>98339</v>
+        <v>78639</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hamrasjöhötjärnen, Hamrasjöhötjärnen, Dlr</t>
+          <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>496225</v>
+        <v>495658</v>
       </c>
       <c r="R8" t="n">
-        <v>6830300</v>
+        <v>6830096</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1378,12 +1378,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>

--- a/artfynd/A 22588-2025 artfynd.xlsx
+++ b/artfynd/A 22588-2025 artfynd.xlsx
@@ -785,54 +785,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125711283</v>
+        <v>125709664</v>
       </c>
       <c r="B3" t="n">
-        <v>98339</v>
+        <v>79591</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>495823</v>
+        <v>495466</v>
       </c>
       <c r="R3" t="n">
-        <v>6830334</v>
+        <v>6830109</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,11 +856,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Inom anmälan A-22588-2025.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,10 +882,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125709664</v>
+        <v>125710600</v>
       </c>
       <c r="B4" t="n">
-        <v>79590</v>
+        <v>78732</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -907,37 +893,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Rickosennoppi, Rickosennoppi, Dlr</t>
+          <t>Hamrasjöhötjärnen, Hamrasjöhötjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>495466</v>
+        <v>496171</v>
       </c>
       <c r="R4" t="n">
-        <v>6830109</v>
+        <v>6830337</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,60 +967,69 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125710600</v>
+        <v>125711283</v>
       </c>
       <c r="B5" t="n">
-        <v>78731</v>
+        <v>98341</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hamrasjöhötjärnen, Hamrasjöhötjärnen, Dlr</t>
+          <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>496171</v>
+        <v>495823</v>
       </c>
       <c r="R5" t="n">
-        <v>6830337</v>
+        <v>6830334</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1064,6 +1059,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Inom anmälan A-22588-2025.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1078,12 +1078,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1093,7 +1093,7 @@
         <v>125710723</v>
       </c>
       <c r="B6" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         <v>125710815</v>
       </c>
       <c r="B7" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
         <v>125710065</v>
       </c>
       <c r="B8" t="n">
-        <v>78639</v>
+        <v>78640</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         <v>125709668</v>
       </c>
       <c r="B9" t="n">
-        <v>78639</v>
+        <v>78640</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         <v>125711141</v>
       </c>
       <c r="B10" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1584,10 +1584,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125710052</v>
+        <v>125709968</v>
       </c>
       <c r="B11" t="n">
-        <v>78731</v>
+        <v>78640</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1595,34 +1595,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Åtjärnen, Åtjärnen, Dlr</t>
+          <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>495635</v>
+        <v>495640</v>
       </c>
       <c r="R11" t="n">
-        <v>6830098</v>
+        <v>6830078</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1669,22 +1669,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125709968</v>
+        <v>125710052</v>
       </c>
       <c r="B12" t="n">
-        <v>78639</v>
+        <v>78732</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1692,34 +1692,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Rickosennoppi, Rickosennoppi, Dlr</t>
+          <t>Åtjärnen, Åtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>495640</v>
+        <v>495635</v>
       </c>
       <c r="R12" t="n">
-        <v>6830078</v>
+        <v>6830098</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1766,22 +1766,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125710983</v>
+        <v>125709636</v>
       </c>
       <c r="B13" t="n">
-        <v>78972</v>
+        <v>78732</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1789,37 +1789,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Hamrasjöhötjärnen, Hamrasjöhötjärnen, Dlr</t>
+          <t>Åtjärnen, Åtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>496064</v>
+        <v>495478</v>
       </c>
       <c r="R13" t="n">
-        <v>6830327</v>
+        <v>6830082</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1875,10 +1875,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125709636</v>
+        <v>125710983</v>
       </c>
       <c r="B14" t="n">
-        <v>78731</v>
+        <v>78973</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1886,37 +1886,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Åtjärnen, Åtjärnen, Dlr</t>
+          <t>Hamrasjöhötjärnen, Hamrasjöhötjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>495478</v>
+        <v>496064</v>
       </c>
       <c r="R14" t="n">
-        <v>6830082</v>
+        <v>6830327</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         <v>125709679</v>
       </c>
       <c r="B15" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         <v>125710834</v>
       </c>
       <c r="B16" t="n">
-        <v>91232</v>
+        <v>91234</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
         <v>125710111</v>
       </c>
       <c r="B17" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
         <v>125710845</v>
       </c>
       <c r="B18" t="n">
-        <v>91197</v>
+        <v>91199</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>125711527</v>
       </c>
       <c r="B19" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 22588-2025 artfynd.xlsx
+++ b/artfynd/A 22588-2025 artfynd.xlsx
@@ -785,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125709664</v>
+        <v>125710600</v>
       </c>
       <c r="B3" t="n">
-        <v>79591</v>
+        <v>78732</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -796,37 +796,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Rickosennoppi, Rickosennoppi, Dlr</t>
+          <t>Hamrasjöhötjärnen, Hamrasjöhötjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>495466</v>
+        <v>496171</v>
       </c>
       <c r="R3" t="n">
-        <v>6830109</v>
+        <v>6830337</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,60 +870,69 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125710600</v>
+        <v>125711283</v>
       </c>
       <c r="B4" t="n">
-        <v>78732</v>
+        <v>98341</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hamrasjöhötjärnen, Hamrasjöhötjärnen, Dlr</t>
+          <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>496171</v>
+        <v>495823</v>
       </c>
       <c r="R4" t="n">
-        <v>6830337</v>
+        <v>6830334</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -953,6 +962,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Inom anmälan A-22588-2025.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -967,66 +981,57 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125711283</v>
+        <v>125709664</v>
       </c>
       <c r="B5" t="n">
-        <v>98341</v>
+        <v>79591</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>495823</v>
+        <v>495466</v>
       </c>
       <c r="R5" t="n">
-        <v>6830334</v>
+        <v>6830109</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1059,11 +1064,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Inom anmälan A-22588-2025.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1584,10 +1584,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125709968</v>
+        <v>125710052</v>
       </c>
       <c r="B11" t="n">
-        <v>78640</v>
+        <v>78732</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1595,34 +1595,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Rickosennoppi, Rickosennoppi, Dlr</t>
+          <t>Åtjärnen, Åtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>495640</v>
+        <v>495635</v>
       </c>
       <c r="R11" t="n">
-        <v>6830078</v>
+        <v>6830098</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1669,22 +1669,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125710052</v>
+        <v>125709968</v>
       </c>
       <c r="B12" t="n">
-        <v>78732</v>
+        <v>78640</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1692,34 +1692,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Åtjärnen, Åtjärnen, Dlr</t>
+          <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>495635</v>
+        <v>495640</v>
       </c>
       <c r="R12" t="n">
-        <v>6830098</v>
+        <v>6830078</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1766,12 +1766,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2069,10 +2069,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125710834</v>
+        <v>125710111</v>
       </c>
       <c r="B16" t="n">
-        <v>91234</v>
+        <v>78732</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2080,21 +2080,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2104,10 +2104,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>496144</v>
+        <v>495675</v>
       </c>
       <c r="R16" t="n">
-        <v>6830386</v>
+        <v>6830131</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2166,10 +2166,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125710111</v>
+        <v>125710834</v>
       </c>
       <c r="B17" t="n">
-        <v>78732</v>
+        <v>91234</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2177,21 +2177,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228912</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2201,10 +2201,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>495675</v>
+        <v>496144</v>
       </c>
       <c r="R17" t="n">
-        <v>6830131</v>
+        <v>6830386</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 22588-2025 artfynd.xlsx
+++ b/artfynd/A 22588-2025 artfynd.xlsx
@@ -785,48 +785,57 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125710600</v>
+        <v>125711283</v>
       </c>
       <c r="B3" t="n">
-        <v>78732</v>
+        <v>98343</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hamrasjöhötjärnen, Hamrasjöhötjärnen, Dlr</t>
+          <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>496171</v>
+        <v>495823</v>
       </c>
       <c r="R3" t="n">
-        <v>6830337</v>
+        <v>6830334</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -856,6 +865,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Inom anmälan A-22588-2025.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -870,69 +884,60 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125711283</v>
+        <v>125710600</v>
       </c>
       <c r="B4" t="n">
-        <v>98341</v>
+        <v>78732</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Rickosennoppi, Rickosennoppi, Dlr</t>
+          <t>Hamrasjöhötjärnen, Hamrasjöhötjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>495823</v>
+        <v>496171</v>
       </c>
       <c r="R4" t="n">
-        <v>6830334</v>
+        <v>6830337</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -962,11 +967,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Inom anmälan A-22588-2025.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,12 +981,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1090,10 +1090,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125710723</v>
+        <v>125710815</v>
       </c>
       <c r="B6" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1118,29 +1118,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Rickosennoppi, Rickosennoppi, Dlr</t>
+          <t>Hamrasjöhötjärnen, Hamrasjöhötjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>496089</v>
+        <v>496225</v>
       </c>
       <c r="R6" t="n">
-        <v>6830292</v>
+        <v>6830300</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1184,60 +1175,60 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125710815</v>
+        <v>125710065</v>
       </c>
       <c r="B7" t="n">
-        <v>98341</v>
+        <v>78640</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hamrasjöhötjärnen, Hamrasjöhötjärnen, Dlr</t>
+          <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>496225</v>
+        <v>495658</v>
       </c>
       <c r="R7" t="n">
-        <v>6830300</v>
+        <v>6830096</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1281,57 +1272,66 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125710065</v>
+        <v>125710723</v>
       </c>
       <c r="B8" t="n">
-        <v>78640</v>
+        <v>98343</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>495658</v>
+        <v>496089</v>
       </c>
       <c r="R8" t="n">
-        <v>6830096</v>
+        <v>6830292</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1584,10 +1584,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125710052</v>
+        <v>125709968</v>
       </c>
       <c r="B11" t="n">
-        <v>78732</v>
+        <v>78640</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1595,34 +1595,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Åtjärnen, Åtjärnen, Dlr</t>
+          <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>495635</v>
+        <v>495640</v>
       </c>
       <c r="R11" t="n">
-        <v>6830098</v>
+        <v>6830078</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1669,22 +1669,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125709968</v>
+        <v>125710052</v>
       </c>
       <c r="B12" t="n">
-        <v>78640</v>
+        <v>78732</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1692,34 +1692,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Rickosennoppi, Rickosennoppi, Dlr</t>
+          <t>Åtjärnen, Åtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>495640</v>
+        <v>495635</v>
       </c>
       <c r="R12" t="n">
-        <v>6830078</v>
+        <v>6830098</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1766,22 +1766,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125709636</v>
+        <v>125710983</v>
       </c>
       <c r="B13" t="n">
-        <v>78732</v>
+        <v>78973</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1789,37 +1789,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Åtjärnen, Åtjärnen, Dlr</t>
+          <t>Hamrasjöhötjärnen, Hamrasjöhötjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>495478</v>
+        <v>496064</v>
       </c>
       <c r="R13" t="n">
-        <v>6830082</v>
+        <v>6830327</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1875,10 +1875,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125710983</v>
+        <v>125709636</v>
       </c>
       <c r="B14" t="n">
-        <v>78973</v>
+        <v>78732</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1886,37 +1886,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Hamrasjöhötjärnen, Hamrasjöhötjärnen, Dlr</t>
+          <t>Åtjärnen, Åtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>496064</v>
+        <v>495478</v>
       </c>
       <c r="R14" t="n">
-        <v>6830327</v>
+        <v>6830082</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2069,10 +2069,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125710111</v>
+        <v>125710834</v>
       </c>
       <c r="B16" t="n">
-        <v>78732</v>
+        <v>91236</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2080,21 +2080,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2104,10 +2104,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>495675</v>
+        <v>496144</v>
       </c>
       <c r="R16" t="n">
-        <v>6830131</v>
+        <v>6830386</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2166,10 +2166,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125710834</v>
+        <v>125710111</v>
       </c>
       <c r="B17" t="n">
-        <v>91234</v>
+        <v>78732</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2177,21 +2177,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>228912</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2201,10 +2201,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>496144</v>
+        <v>495675</v>
       </c>
       <c r="R17" t="n">
-        <v>6830386</v>
+        <v>6830131</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2263,10 +2263,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125710845</v>
+        <v>125711527</v>
       </c>
       <c r="B18" t="n">
-        <v>91199</v>
+        <v>98364</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2274,21 +2274,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>221952</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2298,10 +2298,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>496132</v>
+        <v>495738</v>
       </c>
       <c r="R18" t="n">
-        <v>6830383</v>
+        <v>6830297</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2360,10 +2360,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125711527</v>
+        <v>125710845</v>
       </c>
       <c r="B19" t="n">
-        <v>98362</v>
+        <v>91201</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2371,21 +2371,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221952</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2395,10 +2395,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>495738</v>
+        <v>496132</v>
       </c>
       <c r="R19" t="n">
-        <v>6830297</v>
+        <v>6830383</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 22588-2025 artfynd.xlsx
+++ b/artfynd/A 22588-2025 artfynd.xlsx
@@ -2263,10 +2263,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125711527</v>
+        <v>125710845</v>
       </c>
       <c r="B18" t="n">
-        <v>98364</v>
+        <v>91201</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2274,21 +2274,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221952</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2298,10 +2298,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>495738</v>
+        <v>496132</v>
       </c>
       <c r="R18" t="n">
-        <v>6830297</v>
+        <v>6830383</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2360,10 +2360,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125710845</v>
+        <v>125711527</v>
       </c>
       <c r="B19" t="n">
-        <v>91201</v>
+        <v>98364</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2371,21 +2371,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>221952</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2395,10 +2395,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>496132</v>
+        <v>495738</v>
       </c>
       <c r="R19" t="n">
-        <v>6830383</v>
+        <v>6830297</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 22588-2025 artfynd.xlsx
+++ b/artfynd/A 22588-2025 artfynd.xlsx
@@ -785,54 +785,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125711283</v>
+        <v>125709664</v>
       </c>
       <c r="B3" t="n">
-        <v>98343</v>
+        <v>79591</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>495823</v>
+        <v>495466</v>
       </c>
       <c r="R3" t="n">
-        <v>6830334</v>
+        <v>6830109</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,11 +856,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Inom anmälan A-22588-2025.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,48 +882,57 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125710600</v>
+        <v>125711283</v>
       </c>
       <c r="B4" t="n">
-        <v>78732</v>
+        <v>98345</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hamrasjöhötjärnen, Hamrasjöhötjärnen, Dlr</t>
+          <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>496171</v>
+        <v>495823</v>
       </c>
       <c r="R4" t="n">
-        <v>6830337</v>
+        <v>6830334</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -967,6 +962,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Inom anmälan A-22588-2025.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,22 +981,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125709664</v>
+        <v>125710600</v>
       </c>
       <c r="B5" t="n">
-        <v>79591</v>
+        <v>78732</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1004,37 +1004,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Rickosennoppi, Rickosennoppi, Dlr</t>
+          <t>Hamrasjöhötjärnen, Hamrasjöhötjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>495466</v>
+        <v>496171</v>
       </c>
       <c r="R5" t="n">
-        <v>6830109</v>
+        <v>6830337</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1078,60 +1078,60 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125710815</v>
+        <v>125710065</v>
       </c>
       <c r="B6" t="n">
-        <v>98343</v>
+        <v>78640</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hamrasjöhötjärnen, Hamrasjöhötjärnen, Dlr</t>
+          <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>496225</v>
+        <v>495658</v>
       </c>
       <c r="R6" t="n">
-        <v>6830300</v>
+        <v>6830096</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1175,60 +1175,60 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125710065</v>
+        <v>125710815</v>
       </c>
       <c r="B7" t="n">
-        <v>78640</v>
+        <v>98345</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Rickosennoppi, Rickosennoppi, Dlr</t>
+          <t>Hamrasjöhötjärnen, Hamrasjöhötjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>495658</v>
+        <v>496225</v>
       </c>
       <c r="R7" t="n">
-        <v>6830096</v>
+        <v>6830300</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1272,12 +1272,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1287,7 +1287,7 @@
         <v>125710723</v>
       </c>
       <c r="B8" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1584,10 +1584,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125709968</v>
+        <v>125710052</v>
       </c>
       <c r="B11" t="n">
-        <v>78640</v>
+        <v>78732</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1595,34 +1595,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Rickosennoppi, Rickosennoppi, Dlr</t>
+          <t>Åtjärnen, Åtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>495640</v>
+        <v>495635</v>
       </c>
       <c r="R11" t="n">
-        <v>6830078</v>
+        <v>6830098</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1669,22 +1669,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125710052</v>
+        <v>125709968</v>
       </c>
       <c r="B12" t="n">
-        <v>78732</v>
+        <v>78640</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1692,34 +1692,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Åtjärnen, Åtjärnen, Dlr</t>
+          <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>495635</v>
+        <v>495640</v>
       </c>
       <c r="R12" t="n">
-        <v>6830098</v>
+        <v>6830078</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1766,22 +1766,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125710983</v>
+        <v>125709636</v>
       </c>
       <c r="B13" t="n">
-        <v>78973</v>
+        <v>78732</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1789,37 +1789,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Hamrasjöhötjärnen, Hamrasjöhötjärnen, Dlr</t>
+          <t>Åtjärnen, Åtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>496064</v>
+        <v>495478</v>
       </c>
       <c r="R13" t="n">
-        <v>6830327</v>
+        <v>6830082</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1875,10 +1875,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125709636</v>
+        <v>125710983</v>
       </c>
       <c r="B14" t="n">
-        <v>78732</v>
+        <v>78973</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1886,37 +1886,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Åtjärnen, Åtjärnen, Dlr</t>
+          <t>Hamrasjöhötjärnen, Hamrasjöhötjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>495478</v>
+        <v>496064</v>
       </c>
       <c r="R14" t="n">
-        <v>6830082</v>
+        <v>6830327</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         <v>125710834</v>
       </c>
       <c r="B16" t="n">
-        <v>91236</v>
+        <v>91238</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2263,10 +2263,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125710845</v>
+        <v>125711527</v>
       </c>
       <c r="B18" t="n">
-        <v>91201</v>
+        <v>98366</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2274,21 +2274,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>221952</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2298,10 +2298,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>496132</v>
+        <v>495738</v>
       </c>
       <c r="R18" t="n">
-        <v>6830383</v>
+        <v>6830297</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2360,10 +2360,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125711527</v>
+        <v>125710845</v>
       </c>
       <c r="B19" t="n">
-        <v>98364</v>
+        <v>91203</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2371,21 +2371,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221952</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2395,10 +2395,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>495738</v>
+        <v>496132</v>
       </c>
       <c r="R19" t="n">
-        <v>6830297</v>
+        <v>6830383</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 22588-2025 artfynd.xlsx
+++ b/artfynd/A 22588-2025 artfynd.xlsx
@@ -785,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125709664</v>
+        <v>125710600</v>
       </c>
       <c r="B3" t="n">
-        <v>79591</v>
+        <v>78732</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -796,37 +796,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Rickosennoppi, Rickosennoppi, Dlr</t>
+          <t>Hamrasjöhötjärnen, Hamrasjöhötjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>495466</v>
+        <v>496171</v>
       </c>
       <c r="R3" t="n">
-        <v>6830109</v>
+        <v>6830337</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,66 +870,57 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125711283</v>
+        <v>125709664</v>
       </c>
       <c r="B4" t="n">
-        <v>98345</v>
+        <v>79591</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>495823</v>
+        <v>495466</v>
       </c>
       <c r="R4" t="n">
-        <v>6830334</v>
+        <v>6830109</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -962,11 +953,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Inom anmälan A-22588-2025.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -993,48 +979,57 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125710600</v>
+        <v>125711283</v>
       </c>
       <c r="B5" t="n">
-        <v>78732</v>
+        <v>98345</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hamrasjöhötjärnen, Hamrasjöhötjärnen, Dlr</t>
+          <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>496171</v>
+        <v>495823</v>
       </c>
       <c r="R5" t="n">
-        <v>6830337</v>
+        <v>6830334</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1064,6 +1059,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Inom anmälan A-22588-2025.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1078,12 +1078,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -2263,10 +2263,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125711527</v>
+        <v>125710845</v>
       </c>
       <c r="B18" t="n">
-        <v>98366</v>
+        <v>91203</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2274,21 +2274,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221952</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2298,10 +2298,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>495738</v>
+        <v>496132</v>
       </c>
       <c r="R18" t="n">
-        <v>6830297</v>
+        <v>6830383</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2360,10 +2360,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125710845</v>
+        <v>125711527</v>
       </c>
       <c r="B19" t="n">
-        <v>91203</v>
+        <v>98366</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2371,21 +2371,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>221952</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2395,10 +2395,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>496132</v>
+        <v>495738</v>
       </c>
       <c r="R19" t="n">
-        <v>6830383</v>
+        <v>6830297</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 22588-2025 artfynd.xlsx
+++ b/artfynd/A 22588-2025 artfynd.xlsx
@@ -785,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125710600</v>
+        <v>125709664</v>
       </c>
       <c r="B3" t="n">
-        <v>78732</v>
+        <v>79595</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -796,37 +796,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hamrasjöhötjärnen, Hamrasjöhötjärnen, Dlr</t>
+          <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>496171</v>
+        <v>495466</v>
       </c>
       <c r="R3" t="n">
-        <v>6830337</v>
+        <v>6830109</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,57 +870,66 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125709664</v>
+        <v>125711283</v>
       </c>
       <c r="B4" t="n">
-        <v>79591</v>
+        <v>98349</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>495466</v>
+        <v>495823</v>
       </c>
       <c r="R4" t="n">
-        <v>6830109</v>
+        <v>6830334</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -953,6 +962,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Inom anmälan A-22588-2025.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -979,57 +993,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125711283</v>
+        <v>125710600</v>
       </c>
       <c r="B5" t="n">
-        <v>98345</v>
+        <v>78736</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Rickosennoppi, Rickosennoppi, Dlr</t>
+          <t>Hamrasjöhötjärnen, Hamrasjöhötjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>495823</v>
+        <v>496171</v>
       </c>
       <c r="R5" t="n">
-        <v>6830334</v>
+        <v>6830337</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1059,11 +1064,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Inom anmälan A-22588-2025.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1078,12 +1078,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1093,7 +1093,7 @@
         <v>125710065</v>
       </c>
       <c r="B6" t="n">
-        <v>78640</v>
+        <v>78644</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1187,10 +1187,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125710815</v>
+        <v>125710723</v>
       </c>
       <c r="B7" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1215,20 +1215,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hamrasjöhötjärnen, Hamrasjöhötjärnen, Dlr</t>
+          <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>496225</v>
+        <v>496089</v>
       </c>
       <c r="R7" t="n">
-        <v>6830300</v>
+        <v>6830292</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1272,22 +1281,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125710723</v>
+        <v>125710815</v>
       </c>
       <c r="B8" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1312,29 +1321,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Rickosennoppi, Rickosennoppi, Dlr</t>
+          <t>Hamrasjöhötjärnen, Hamrasjöhötjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>496089</v>
+        <v>496225</v>
       </c>
       <c r="R8" t="n">
-        <v>6830292</v>
+        <v>6830300</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1378,12 +1378,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1393,7 +1393,7 @@
         <v>125709668</v>
       </c>
       <c r="B9" t="n">
-        <v>78640</v>
+        <v>78644</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         <v>125711141</v>
       </c>
       <c r="B10" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1584,10 +1584,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125710052</v>
+        <v>125709968</v>
       </c>
       <c r="B11" t="n">
-        <v>78732</v>
+        <v>78644</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1595,34 +1595,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Åtjärnen, Åtjärnen, Dlr</t>
+          <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>495635</v>
+        <v>495640</v>
       </c>
       <c r="R11" t="n">
-        <v>6830098</v>
+        <v>6830078</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1669,22 +1669,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125709968</v>
+        <v>125710052</v>
       </c>
       <c r="B12" t="n">
-        <v>78640</v>
+        <v>78736</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1692,34 +1692,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Rickosennoppi, Rickosennoppi, Dlr</t>
+          <t>Åtjärnen, Åtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>495640</v>
+        <v>495635</v>
       </c>
       <c r="R12" t="n">
-        <v>6830078</v>
+        <v>6830098</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1766,22 +1766,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125709636</v>
+        <v>125710983</v>
       </c>
       <c r="B13" t="n">
-        <v>78732</v>
+        <v>78977</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1789,37 +1789,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Åtjärnen, Åtjärnen, Dlr</t>
+          <t>Hamrasjöhötjärnen, Hamrasjöhötjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>495478</v>
+        <v>496064</v>
       </c>
       <c r="R13" t="n">
-        <v>6830082</v>
+        <v>6830327</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1875,10 +1875,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125710983</v>
+        <v>125709636</v>
       </c>
       <c r="B14" t="n">
-        <v>78973</v>
+        <v>78736</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1886,37 +1886,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Hamrasjöhötjärnen, Hamrasjöhötjärnen, Dlr</t>
+          <t>Åtjärnen, Åtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>496064</v>
+        <v>495478</v>
       </c>
       <c r="R14" t="n">
-        <v>6830327</v>
+        <v>6830082</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         <v>125709679</v>
       </c>
       <c r="B15" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         <v>125710834</v>
       </c>
       <c r="B16" t="n">
-        <v>91238</v>
+        <v>91242</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
         <v>125710111</v>
       </c>
       <c r="B17" t="n">
-        <v>78732</v>
+        <v>78736</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2263,10 +2263,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125710845</v>
+        <v>125711527</v>
       </c>
       <c r="B18" t="n">
-        <v>91203</v>
+        <v>98370</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2274,21 +2274,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>221952</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2298,10 +2298,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>496132</v>
+        <v>495738</v>
       </c>
       <c r="R18" t="n">
-        <v>6830383</v>
+        <v>6830297</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2360,10 +2360,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125711527</v>
+        <v>125710845</v>
       </c>
       <c r="B19" t="n">
-        <v>98366</v>
+        <v>91207</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2371,21 +2371,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221952</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2395,10 +2395,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>495738</v>
+        <v>496132</v>
       </c>
       <c r="R19" t="n">
-        <v>6830297</v>
+        <v>6830383</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 22588-2025 artfynd.xlsx
+++ b/artfynd/A 22588-2025 artfynd.xlsx
@@ -785,45 +785,54 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125709664</v>
+        <v>125711283</v>
       </c>
       <c r="B3" t="n">
-        <v>79595</v>
+        <v>98352</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>495466</v>
+        <v>495823</v>
       </c>
       <c r="R3" t="n">
-        <v>6830109</v>
+        <v>6830334</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -856,6 +865,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Inom anmälan A-22588-2025.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -882,57 +896,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125711283</v>
+        <v>125710600</v>
       </c>
       <c r="B4" t="n">
-        <v>98349</v>
+        <v>78736</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Rickosennoppi, Rickosennoppi, Dlr</t>
+          <t>Hamrasjöhötjärnen, Hamrasjöhötjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>495823</v>
+        <v>496171</v>
       </c>
       <c r="R4" t="n">
-        <v>6830334</v>
+        <v>6830337</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -962,11 +967,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Inom anmälan A-22588-2025.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,22 +981,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125710600</v>
+        <v>125709664</v>
       </c>
       <c r="B5" t="n">
-        <v>78736</v>
+        <v>79595</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1004,37 +1004,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hamrasjöhötjärnen, Hamrasjöhötjärnen, Dlr</t>
+          <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>496171</v>
+        <v>495466</v>
       </c>
       <c r="R5" t="n">
-        <v>6830337</v>
+        <v>6830109</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1078,12 +1078,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1187,10 +1187,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125710723</v>
+        <v>125710815</v>
       </c>
       <c r="B7" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1215,29 +1215,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Rickosennoppi, Rickosennoppi, Dlr</t>
+          <t>Hamrasjöhötjärnen, Hamrasjöhötjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>496089</v>
+        <v>496225</v>
       </c>
       <c r="R7" t="n">
-        <v>6830292</v>
+        <v>6830300</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1281,22 +1272,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125710815</v>
+        <v>125710723</v>
       </c>
       <c r="B8" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1321,20 +1312,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hamrasjöhötjärnen, Hamrasjöhötjärnen, Dlr</t>
+          <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>496225</v>
+        <v>496089</v>
       </c>
       <c r="R8" t="n">
-        <v>6830300</v>
+        <v>6830292</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1378,12 +1378,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -2263,10 +2263,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125711527</v>
+        <v>125710845</v>
       </c>
       <c r="B18" t="n">
-        <v>98370</v>
+        <v>91207</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2274,21 +2274,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221952</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2298,10 +2298,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>495738</v>
+        <v>496132</v>
       </c>
       <c r="R18" t="n">
-        <v>6830297</v>
+        <v>6830383</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2360,10 +2360,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125710845</v>
+        <v>125711527</v>
       </c>
       <c r="B19" t="n">
-        <v>91207</v>
+        <v>98373</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2371,21 +2371,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>221952</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2395,10 +2395,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>496132</v>
+        <v>495738</v>
       </c>
       <c r="R19" t="n">
-        <v>6830383</v>
+        <v>6830297</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 22588-2025 artfynd.xlsx
+++ b/artfynd/A 22588-2025 artfynd.xlsx
@@ -785,57 +785,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125711283</v>
+        <v>125710600</v>
       </c>
       <c r="B3" t="n">
-        <v>98352</v>
+        <v>78736</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Rickosennoppi, Rickosennoppi, Dlr</t>
+          <t>Hamrasjöhötjärnen, Hamrasjöhötjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>495823</v>
+        <v>496171</v>
       </c>
       <c r="R3" t="n">
-        <v>6830334</v>
+        <v>6830337</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -865,11 +856,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Inom anmälan A-22588-2025.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,22 +870,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125710600</v>
+        <v>125709664</v>
       </c>
       <c r="B4" t="n">
-        <v>78736</v>
+        <v>79595</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -907,37 +893,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hamrasjöhötjärnen, Hamrasjöhötjärnen, Dlr</t>
+          <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>496171</v>
+        <v>495466</v>
       </c>
       <c r="R4" t="n">
-        <v>6830337</v>
+        <v>6830109</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,57 +967,66 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125709664</v>
+        <v>125711283</v>
       </c>
       <c r="B5" t="n">
-        <v>79595</v>
+        <v>98352</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>495466</v>
+        <v>495823</v>
       </c>
       <c r="R5" t="n">
-        <v>6830109</v>
+        <v>6830334</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1064,6 +1059,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Inom anmälan A-22588-2025.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1090,48 +1090,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125710065</v>
+        <v>125710815</v>
       </c>
       <c r="B6" t="n">
-        <v>78644</v>
+        <v>98352</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Rickosennoppi, Rickosennoppi, Dlr</t>
+          <t>Hamrasjöhötjärnen, Hamrasjöhötjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>495658</v>
+        <v>496225</v>
       </c>
       <c r="R6" t="n">
-        <v>6830096</v>
+        <v>6830300</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1175,19 +1175,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125710815</v>
+        <v>125710723</v>
       </c>
       <c r="B7" t="n">
         <v>98352</v>
@@ -1215,20 +1215,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hamrasjöhötjärnen, Hamrasjöhötjärnen, Dlr</t>
+          <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>496225</v>
+        <v>496089</v>
       </c>
       <c r="R7" t="n">
-        <v>6830300</v>
+        <v>6830292</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1272,66 +1281,57 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125710723</v>
+        <v>125710065</v>
       </c>
       <c r="B8" t="n">
-        <v>98352</v>
+        <v>78644</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Rickosennoppi, Rickosennoppi, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>496089</v>
+        <v>495658</v>
       </c>
       <c r="R8" t="n">
-        <v>6830292</v>
+        <v>6830096</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -2263,10 +2263,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125710845</v>
+        <v>125711527</v>
       </c>
       <c r="B18" t="n">
-        <v>91207</v>
+        <v>98373</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2274,21 +2274,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>221952</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2298,10 +2298,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>496132</v>
+        <v>495738</v>
       </c>
       <c r="R18" t="n">
-        <v>6830383</v>
+        <v>6830297</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2360,10 +2360,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125711527</v>
+        <v>125710845</v>
       </c>
       <c r="B19" t="n">
-        <v>98373</v>
+        <v>91207</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2371,21 +2371,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221952</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2395,10 +2395,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>495738</v>
+        <v>496132</v>
       </c>
       <c r="R19" t="n">
-        <v>6830297</v>
+        <v>6830383</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
